--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-patient.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-patient.xlsx
@@ -1843,7 +1843,7 @@
   <si>
     <t>複数のユースケースがある。  
 　- 事務的なエラーのため一貫して人間を特定することが困難であり患者の記録が重複している  
-　- 複数のサーバにわたり患者情報が配布されている</t>
+　- 複数のサーバーにわたり患者情報が配布されている</t>
   </si>
   <si>
     <t>outboundLink</t>
